--- a/data/05_modelado/results/results_lineales_completo.xlsx
+++ b/data/05_modelado/results/results_lineales_completo.xlsx
@@ -533,12 +533,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SVM_RBF</t>
+          <t>SGDElasticNet</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>smote</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,68 +547,68 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7564983454614655</v>
+        <v>0.7498507807360217</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006123515596986275</v>
+        <v>0.006027893023129959</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9055556282596344</v>
+        <v>0.9080340040199995</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003415658412659005</v>
+        <v>0.003540900512979701</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7119822164425902</v>
+        <v>0.6816717829089194</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8071431744875202</v>
+        <v>0.8333322562847802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8480070299547116</v>
+        <v>0.8373736705665914</v>
       </c>
       <c r="K2" t="n">
-        <v>112.901</v>
+        <v>4.623</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7623</v>
+        <v>0.755</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9142</v>
+        <v>0.9134</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7079</v>
+        <v>0.6817</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8256</v>
+        <v>0.846</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8494</v>
+        <v>0.8394</v>
       </c>
       <c r="R2" t="n">
-        <v>0.653</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3252</v>
+        <v>0.383</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>basico</t>
+          <t>ext</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SVM_RBF</t>
+          <t>SGDElasticNet</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>smote</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,56 +617,56 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7582709660512823</v>
+        <v>0.747327937025999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004171604488190237</v>
+        <v>0.01376937941294494</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9032101966333258</v>
+        <v>0.9058661087149359</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00242878605028493</v>
+        <v>0.004884769542416435</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7225322042312822</v>
+        <v>0.6852618333117529</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7979907928504441</v>
+        <v>0.8231616598718366</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8511674686979726</v>
+        <v>0.8369655157638372</v>
       </c>
       <c r="K3" t="n">
-        <v>448.563</v>
+        <v>0.764</v>
       </c>
       <c r="L3" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7613</v>
+        <v>0.7605</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9126</v>
+        <v>0.9132</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7163</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8124</v>
+        <v>0.8185</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.851</v>
+        <v>0.8492</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6536</v>
+        <v>0.6513</v>
       </c>
       <c r="S3" t="n">
-        <v>0.357</v>
+        <v>0.3624</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>basico</t>
+          <t>ext</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -687,52 +687,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7400158105610716</v>
+        <v>0.7564983454614655</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001999545657618309</v>
+        <v>0.006123515596986275</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9000351655149885</v>
+        <v>0.9055556282596344</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00386559300205514</v>
+        <v>0.003415658412659005</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8241293282827232</v>
+        <v>0.7119822164425902</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6716241595992087</v>
+        <v>0.8071431744875202</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8619868675580584</v>
+        <v>0.8480070299547116</v>
       </c>
       <c r="K4" t="n">
-        <v>109.93</v>
+        <v>112.901</v>
       </c>
       <c r="L4" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7541</v>
+        <v>0.7623</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9083</v>
+        <v>0.9142</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8293</v>
+        <v>0.7079</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6914</v>
+        <v>0.8256</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8681</v>
+        <v>0.8494</v>
       </c>
       <c r="R4" t="n">
-        <v>0.665</v>
+        <v>0.653</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3283</v>
+        <v>0.3252</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -743,12 +743,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SGDElasticNet</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -757,63 +757,63 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7215904896594297</v>
+        <v>0.7393836496871475</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00357759049344102</v>
+        <v>0.007832908049006399</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8850984813019854</v>
+        <v>0.9051599001258989</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004869039549467532</v>
+        <v>0.003946958430842508</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6528527229086913</v>
+        <v>0.7825349652936302</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8067637572084841</v>
+        <v>0.7017556429939472</v>
       </c>
       <c r="J5" t="n">
-        <v>0.81796543213972</v>
+        <v>0.8552946160581802</v>
       </c>
       <c r="K5" t="n">
-        <v>6.807</v>
+        <v>0.822</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7288</v>
+        <v>0.7494</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8912</v>
+        <v>0.9069</v>
       </c>
       <c r="O5" t="n">
-        <v>0.653</v>
+        <v>0.8022</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8246</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8205</v>
+        <v>0.8625</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5974</v>
+        <v>0.6552</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4183</v>
+        <v>0.3398</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>basico</t>
+          <t>ext</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -827,68 +827,68 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7236380792058493</v>
+        <v>0.7359116552775953</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003262651308187069</v>
+        <v>0.007200138561096124</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8850131604431113</v>
+        <v>0.9038660096861791</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004830727805954928</v>
+        <v>0.00580205681122376</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6592766700839555</v>
+        <v>0.6491643590957055</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8021871624967385</v>
+        <v>0.849860858790049</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8208282657809421</v>
+        <v>0.821571559783296</v>
       </c>
       <c r="K6" t="n">
-        <v>6.385</v>
+        <v>3.093</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M6" t="n">
-        <v>0.731</v>
+        <v>0.7337</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8911</v>
+        <v>0.9001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6581</v>
+        <v>0.6777</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.7997</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.823</v>
+        <v>0.8302</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6016</v>
+        <v>0.6103</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4137</v>
+        <v>0.6812</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>basico</t>
+          <t>ext</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>SVM_RBF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>smote</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -897,63 +897,63 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7145404289681895</v>
+        <v>0.7582709660512823</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008917274356960362</v>
+        <v>0.004171604488190237</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8846695588558642</v>
+        <v>0.9032101966333258</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004505009475381636</v>
+        <v>0.00242878605028493</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7652063442951079</v>
+        <v>0.7225322042312822</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6704800916999138</v>
+        <v>0.7979907928504441</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8433965973968711</v>
+        <v>0.8511674686979726</v>
       </c>
       <c r="K7" t="n">
-        <v>0.445</v>
+        <v>448.563</v>
       </c>
       <c r="L7" t="n">
         <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7209</v>
+        <v>0.7613</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8902</v>
+        <v>0.9126</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7578</v>
+        <v>0.7163</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6873</v>
+        <v>0.8124</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.851</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6133</v>
+        <v>0.6536</v>
       </c>
       <c r="S7" t="n">
-        <v>0.368</v>
+        <v>0.357</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>ext</t>
+          <t>basico</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>SVM_RBF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -967,52 +967,52 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7200656311241855</v>
+        <v>0.7400158105610716</v>
       </c>
       <c r="E8" t="n">
-        <v>0.009654675623845083</v>
+        <v>0.001999545657618309</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8845935644281168</v>
+        <v>0.9000351655149885</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004943200072061573</v>
+        <v>0.00386559300205514</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7756228114556811</v>
+        <v>0.8241293282827232</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6721329842618973</v>
+        <v>0.6716241595992087</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8472262225880488</v>
+        <v>0.8619868675580584</v>
       </c>
       <c r="K8" t="n">
-        <v>5.926</v>
+        <v>109.93</v>
       </c>
       <c r="L8" t="n">
-        <v>5.32</v>
+        <v>5.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7222</v>
+        <v>0.7541</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8911</v>
+        <v>0.9083</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7658</v>
+        <v>0.8293</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6833</v>
+        <v>0.6914</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8462</v>
+        <v>0.8681</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.665</v>
       </c>
       <c r="S8" t="n">
-        <v>0.365</v>
+        <v>0.3283</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1023,12 +1023,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SVM_lineal</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1037,68 +1037,68 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7255033237336189</v>
+        <v>0.7267192283247618</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006104318062521838</v>
+        <v>0.01577460752560449</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8843576981597293</v>
+        <v>0.8997149781030049</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004359519374954015</v>
+        <v>0.004231156829102635</v>
       </c>
       <c r="H9" t="n">
-        <v>0.664561018718131</v>
+        <v>0.7864884931006975</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7990083613971797</v>
+        <v>0.6805268544554671</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8232077312915227</v>
+        <v>0.8509814845146796</v>
       </c>
       <c r="K9" t="n">
-        <v>222.988</v>
+        <v>18.532</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7307</v>
+        <v>0.7271</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8894</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6602</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.6914</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8236</v>
+        <v>0.8482</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6018</v>
+        <v>0.6223</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3695</v>
+        <v>0.7409</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>basico</t>
+          <t>ext</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>smote</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1107,52 +1107,52 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7251676987783179</v>
+        <v>0.7261581011517647</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00612483718205405</v>
+        <v>0.01875638316318416</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8843344284988561</v>
+        <v>0.8904495092967712</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004410697646695203</v>
+        <v>0.0127432871352812</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6614818404456562</v>
+        <v>0.6575439998429703</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8026950178157295</v>
+        <v>0.8189757914489345</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8220923307009015</v>
+        <v>0.8190070569079394</v>
       </c>
       <c r="K10" t="n">
-        <v>2.828</v>
+        <v>2.54</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7287</v>
+        <v>0.7156</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8898</v>
+        <v>0.8931</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.6206</v>
       </c>
       <c r="P10" t="n">
-        <v>0.82</v>
+        <v>0.8449</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8214</v>
+        <v>0.8036</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5981</v>
+        <v>0.5709</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4163</v>
+        <v>0.8991</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1163,12 +1163,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LDA</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>smote</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1177,52 +1177,52 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.7249502786152631</v>
+        <v>0.7215904896594297</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00626459617405727</v>
+        <v>0.00357759049344102</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8843329932241243</v>
+        <v>0.8850984813019854</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004412754167309445</v>
+        <v>0.004869039549467532</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6599831817691921</v>
+        <v>0.6528527229086913</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8043477488204299</v>
+        <v>0.8067637572084841</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8215346269500488</v>
+        <v>0.81796543213972</v>
       </c>
       <c r="K11" t="n">
-        <v>3.107</v>
+        <v>6.807</v>
       </c>
       <c r="L11" t="n">
         <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>0.728</v>
+        <v>0.7288</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8898</v>
+        <v>0.8912</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6538</v>
+        <v>0.653</v>
       </c>
       <c r="P11" t="n">
-        <v>0.821</v>
+        <v>0.8246</v>
       </c>
       <c r="Q11" t="n">
         <v>0.8205</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5966</v>
+        <v>0.5974</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4215</v>
+        <v>0.4183</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SVM_lineal</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1247,52 +1247,52 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7266021910022269</v>
+        <v>0.7236380792058493</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005461443680121344</v>
+        <v>0.003262651308187069</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8839391384077853</v>
+        <v>0.8850131604431113</v>
       </c>
       <c r="G12" t="n">
-        <v>0.00432949259336935</v>
+        <v>0.004830727805954928</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6664119892739955</v>
+        <v>0.6592766700839555</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7990086845117457</v>
+        <v>0.8021871624967385</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8241744813749741</v>
+        <v>0.8208282657809421</v>
       </c>
       <c r="K12" t="n">
-        <v>313.818</v>
+        <v>6.385</v>
       </c>
       <c r="L12" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7322</v>
+        <v>0.731</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8892</v>
+        <v>0.8911</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6627</v>
+        <v>0.6581</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.825</v>
+        <v>0.823</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.6016</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4181</v>
+        <v>0.4137</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SVM_lineal</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1317,52 +1317,52 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.7198124238707404</v>
+        <v>0.7200656311241855</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008186755279267368</v>
+        <v>0.009654675623845083</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8829966625011728</v>
+        <v>0.8845935644281168</v>
       </c>
       <c r="G13" t="n">
-        <v>0.004634565943259712</v>
+        <v>0.004943200072061573</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7781570502099299</v>
+        <v>0.7756228114556811</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6698444445701002</v>
+        <v>0.6721329842618973</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8475608849228481</v>
+        <v>0.8472262225880488</v>
       </c>
       <c r="K13" t="n">
-        <v>196.844</v>
+        <v>5.926</v>
       </c>
       <c r="L13" t="n">
-        <v>5.14</v>
+        <v>5.32</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7236</v>
+        <v>0.7222</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8898</v>
+        <v>0.8911</v>
       </c>
       <c r="O13" t="n">
-        <v>0.773</v>
+        <v>0.7658</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6802</v>
+        <v>0.6833</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.848</v>
+        <v>0.8462</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6194</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3656</v>
+        <v>0.365</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1373,12 +1373,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ridge</t>
+          <t>SVM_lineal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1387,56 +1387,56 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.7116779433492628</v>
+        <v>0.7255033237336189</v>
       </c>
       <c r="E14" t="n">
-        <v>0.008854312699560982</v>
+        <v>0.006104318062521838</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8823283036933158</v>
+        <v>0.8843576981597293</v>
       </c>
       <c r="G14" t="n">
-        <v>0.004433864610869031</v>
+        <v>0.004359519374954015</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7700876878870713</v>
+        <v>0.664561018718131</v>
       </c>
       <c r="I14" t="n">
-        <v>0.661835807717753</v>
+        <v>0.7990083613971797</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8432479607118694</v>
+        <v>0.8232077312915227</v>
       </c>
       <c r="K14" t="n">
-        <v>0.525</v>
+        <v>222.988</v>
       </c>
       <c r="L14" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7205</v>
+        <v>0.7307</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8887</v>
+        <v>0.8894</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7651</v>
+        <v>0.6602</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6807</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8455</v>
+        <v>0.8236</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6142</v>
+        <v>0.6018</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3681</v>
+        <v>0.3695</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>ext</t>
+          <t>basico</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>smote</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1457,52 +1457,52 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.714960077452233</v>
+        <v>0.7249502786152631</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01017420782088104</v>
+        <v>0.00626459617405727</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8823181498223265</v>
+        <v>0.8843329932241243</v>
       </c>
       <c r="G15" t="n">
-        <v>0.004427890999659801</v>
+        <v>0.004412754167309445</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7588041582669012</v>
+        <v>0.6599831817691921</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6762009966468786</v>
+        <v>0.8043477488204299</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8423927486141547</v>
+        <v>0.8215346269500488</v>
       </c>
       <c r="K15" t="n">
-        <v>4.421</v>
+        <v>3.107</v>
       </c>
       <c r="L15" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>0.726</v>
+        <v>0.728</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8887</v>
+        <v>0.8898</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7599</v>
+        <v>0.6538</v>
       </c>
       <c r="P15" t="n">
-        <v>0.695</v>
+        <v>0.821</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8465</v>
+        <v>0.8205</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6197</v>
+        <v>0.5966</v>
       </c>
       <c r="S15" t="n">
-        <v>0.37</v>
+        <v>0.4215</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1513,12 +1513,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LDA</t>
+          <t>SVM_lineal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>smote</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1527,52 +1527,52 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.714960077452233</v>
+        <v>0.7266021910022269</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01017420782088104</v>
+        <v>0.005461443680121344</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8823181498223265</v>
+        <v>0.8839391384077853</v>
       </c>
       <c r="G16" t="n">
-        <v>0.004427890999659801</v>
+        <v>0.00432949259336935</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7588041582669012</v>
+        <v>0.6664119892739955</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6762009966468786</v>
+        <v>0.7990086845117457</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8423927486141547</v>
+        <v>0.8241744813749741</v>
       </c>
       <c r="K16" t="n">
-        <v>5.021</v>
+        <v>313.818</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>5.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0.726</v>
+        <v>0.7322</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8887</v>
+        <v>0.8892</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7599</v>
+        <v>0.6627</v>
       </c>
       <c r="P16" t="n">
-        <v>0.695</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.8465</v>
+        <v>0.825</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6197</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>0.37</v>
+        <v>0.4181</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>Perceptron</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1597,52 +1597,52 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7131382162666238</v>
+        <v>0.7158664191688076</v>
       </c>
       <c r="E17" t="n">
-        <v>0.003093239870022109</v>
+        <v>0.00986043738027908</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8741241306358422</v>
+        <v>0.8832410336398798</v>
       </c>
       <c r="G17" t="n">
-        <v>0.005511197211547377</v>
+        <v>0.007139590517034026</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6465284319982184</v>
+        <v>0.6531384758078419</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7962127741728066</v>
+        <v>0.7923979220502264</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8126486107684366</v>
+        <v>0.8160317315513794</v>
       </c>
       <c r="K17" t="n">
-        <v>4.999</v>
+        <v>8.765000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7187</v>
+        <v>0.7274</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8861</v>
+        <v>0.8915</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6519</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8119</v>
+        <v>0.8226</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.8141</v>
+        <v>0.8196</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5826</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8823</v>
+        <v>0.4494</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>SVM_lineal</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1667,68 +1667,68 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.6941913512113745</v>
+        <v>0.7198124238707404</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01006942602794927</v>
+        <v>0.008186755279267368</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8661494164195437</v>
+        <v>0.8829966625011728</v>
       </c>
       <c r="G18" t="n">
-        <v>0.00671958876914109</v>
+        <v>0.004634565943259712</v>
       </c>
       <c r="H18" t="n">
-        <v>0.730478335432205</v>
+        <v>0.7781570502099299</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6628575767538456</v>
+        <v>0.6698444445701002</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8294168772819536</v>
+        <v>0.8475608849228481</v>
       </c>
       <c r="K18" t="n">
-        <v>5.234</v>
+        <v>196.844</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7084</v>
+        <v>0.7236</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8783</v>
+        <v>0.8898</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7476</v>
+        <v>0.773</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6731</v>
+        <v>0.6802</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.8379</v>
+        <v>0.848</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5966</v>
+        <v>0.6194</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.3656</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>ext</t>
+          <t>basico</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>LDA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>balanced</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1737,68 +1737,68 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.6959085906644356</v>
+        <v>0.714960077452233</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01949689649156733</v>
+        <v>0.01017420782088104</v>
       </c>
       <c r="F19" t="n">
-        <v>0.863202763096637</v>
+        <v>0.8823181498223265</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01055555723602859</v>
+        <v>0.004427890999659801</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6248996621655765</v>
+        <v>0.7588041582669012</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7878241545909329</v>
+        <v>0.6762009966468786</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7979611472675993</v>
+        <v>0.8423927486141547</v>
       </c>
       <c r="K19" t="n">
-        <v>5.38</v>
+        <v>4.421</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6918</v>
+        <v>0.726</v>
       </c>
       <c r="N19" t="n">
-        <v>0.87</v>
+        <v>0.8887</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.7599</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7931</v>
+        <v>0.695</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.7933</v>
+        <v>0.8465</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5401</v>
+        <v>0.6197</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2521</v>
+        <v>0.37</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>ext</t>
+          <t>basico</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Perceptron</t>
+          <t>LDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>balanced</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1807,56 +1807,56 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.5867712130180907</v>
+        <v>0.714960077452233</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03591590599266724</v>
+        <v>0.01017420782088104</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8488396124380351</v>
+        <v>0.8823181498223265</v>
       </c>
       <c r="G20" t="n">
-        <v>0.008353262699786791</v>
+        <v>0.004427890999659801</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8153247288753673</v>
+        <v>0.7588041582669012</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4600861423432753</v>
+        <v>0.6762009966468786</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8115336524871954</v>
+        <v>0.8423927486141547</v>
       </c>
       <c r="K20" t="n">
-        <v>5.942</v>
+        <v>5.021</v>
       </c>
       <c r="L20" t="n">
-        <v>5.32</v>
+        <v>5</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4452</v>
+        <v>0.726</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8433</v>
+        <v>0.8887</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7376</v>
+        <v>0.7599</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3188</v>
+        <v>0.695</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.8465</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3262</v>
+        <v>0.6197</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4671</v>
+        <v>0.37</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>ext</t>
+          <t>basico</t>
         </is>
       </c>
     </row>
@@ -1877,52 +1877,52 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.4857065282087784</v>
+        <v>0.6319948658525671</v>
       </c>
       <c r="E21" t="n">
-        <v>0.03844693262637554</v>
+        <v>0.0390039191867483</v>
       </c>
       <c r="F21" t="n">
-        <v>0.848525965825041</v>
+        <v>0.869424006109857</v>
       </c>
       <c r="G21" t="n">
-        <v>0.004987952975853188</v>
+        <v>0.0218725251244608</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7984896368776917</v>
+        <v>0.7954658103754625</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3517710313251493</v>
+        <v>0.5260559585960995</v>
       </c>
       <c r="J21" t="n">
-        <v>0.783611276401205</v>
+        <v>0.8214975628062042</v>
       </c>
       <c r="K21" t="n">
-        <v>6.822</v>
+        <v>8.106</v>
       </c>
       <c r="L21" t="n">
-        <v>5</v>
+        <v>6.64</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4648</v>
+        <v>0.4465</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8502</v>
+        <v>0.8597</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7408</v>
+        <v>0.716</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3386</v>
+        <v>0.3244</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.7719</v>
+        <v>0.7648</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3445</v>
+        <v>0.323</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4769</v>
+        <v>0.4591</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>smote</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1947,52 +1947,52 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.6701084643253468</v>
+        <v>0.6224816539270621</v>
       </c>
       <c r="E22" t="n">
-        <v>0.02069116428210701</v>
+        <v>0.04430817190313216</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8426267344924778</v>
+        <v>0.8692919612377658</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01293406320725295</v>
+        <v>0.009158002606966488</v>
       </c>
       <c r="H22" t="n">
-        <v>0.599996685635648</v>
+        <v>0.8075223176092313</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7598566502228279</v>
+        <v>0.5100422391516304</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7809721061736022</v>
+        <v>0.8206423576195739</v>
       </c>
       <c r="K22" t="n">
-        <v>5.913</v>
+        <v>5.042</v>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
+        <v>6.9</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6731</v>
+        <v>0.5841</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8339</v>
+        <v>0.855</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6014</v>
+        <v>0.7534</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7641</v>
+        <v>0.4769</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.7829</v>
+        <v>0.8013</v>
       </c>
       <c r="R22" t="n">
-        <v>0.514</v>
+        <v>0.4621</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5302</v>
+        <v>0.4427</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
